--- a/request_forms/012_sender_and_recipient_information_form--request_forms.xlsx
+++ b/request_forms/012_sender_and_recipient_information_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -918,8 +918,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -947,12 +947,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_14,_'label':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 14, 'label': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_15,_'label':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 15, 'label': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_16,_'label':_'mary_smith'}</t>
+          <t>mary_smith</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 16, 'label': 'Mary Smith'}</t>
+          <t>Mary Smith</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_18,_'label':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 18, 'label': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_19,_'label':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 19, 'label': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_20,_'label':_'mary_smith'}</t>
+          <t>mary_smith</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 20, 'label': 'Mary Smith'}</t>
+          <t>Mary Smith</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_22,_'label':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 22, 'label': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_23,_'label':_'in_person'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 23, 'label': 'In Person'}</t>
+          <t>In Person</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_24,_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 24, 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_26,_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 26, 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_27,_'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 27, 'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_28,_'label':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 28, 'label': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_29,_'label':_'scheduled'}</t>
+          <t>scheduled</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 29, 'label': 'Scheduled'}</t>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
